--- a/students.xlsx
+++ b/students.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\반편성\최종\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F22605-DAE4-4D80-829A-049594372DF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE8782DB-EF70-4027-8EEE-00A276E1BBB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E82CF06-4291-4BB2-932B-E63723969F27}"/>
   </bookViews>
@@ -897,9 +897,6 @@
     <t>나한나</t>
   </si>
   <si>
-    <t>김채현</t>
-  </si>
-  <si>
     <t>송나윤</t>
   </si>
   <si>
@@ -1259,6 +1256,10 @@
   </si>
   <si>
     <t>7반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김채현</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1290,7 +1291,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1305,6 +1306,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1338,7 +1345,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1362,6 +1369,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2138,7 +2154,7 @@
         <v>237</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -2295,7 +2311,7 @@
         <v>107</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
@@ -2306,7 +2322,7 @@
         <v>108</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
@@ -2317,7 +2333,7 @@
         <v>109</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.4">
@@ -2328,7 +2344,7 @@
         <v>110</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.4">
@@ -2339,7 +2355,7 @@
         <v>111</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.4">
@@ -2350,7 +2366,7 @@
         <v>112</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
@@ -2361,7 +2377,7 @@
         <v>113</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
@@ -2372,7 +2388,7 @@
         <v>114</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
@@ -2383,7 +2399,7 @@
         <v>115</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
@@ -2394,7 +2410,7 @@
         <v>116</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
@@ -2405,7 +2421,7 @@
         <v>117</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.4">
@@ -2416,7 +2432,7 @@
         <v>118</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.4">
@@ -2427,7 +2443,7 @@
         <v>119</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
@@ -2438,7 +2454,7 @@
         <v>120</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.4">
@@ -2449,7 +2465,7 @@
         <v>121</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.4">
@@ -2460,7 +2476,7 @@
         <v>122</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.4">
@@ -2471,7 +2487,7 @@
         <v>123</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.4">
@@ -2482,7 +2498,7 @@
         <v>124</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
@@ -2493,7 +2509,7 @@
         <v>125</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.4">
@@ -2504,7 +2520,7 @@
         <v>126</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.4">
@@ -2515,7 +2531,7 @@
         <v>127</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
@@ -2526,7 +2542,7 @@
         <v>128</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.4">
@@ -2537,7 +2553,7 @@
         <v>129</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.4">
@@ -2548,7 +2564,7 @@
         <v>130</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
@@ -2559,7 +2575,7 @@
         <v>131</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.4">
@@ -2570,7 +2586,7 @@
         <v>31</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
@@ -2581,7 +2597,7 @@
         <v>155</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.4">
@@ -2592,7 +2608,7 @@
         <v>156</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.4">
@@ -2603,7 +2619,7 @@
         <v>157</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.4">
@@ -2614,7 +2630,7 @@
         <v>158</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.4">
@@ -2625,7 +2641,7 @@
         <v>159</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.4">
@@ -2636,7 +2652,7 @@
         <v>160</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.4">
@@ -2647,7 +2663,7 @@
         <v>161</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.4">
@@ -2658,7 +2674,7 @@
         <v>162</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.4">
@@ -2669,7 +2685,7 @@
         <v>163</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.4">
@@ -2680,7 +2696,7 @@
         <v>164</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.4">
@@ -2691,7 +2707,7 @@
         <v>165</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.4">
@@ -2702,7 +2718,7 @@
         <v>166</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.4">
@@ -2713,7 +2729,7 @@
         <v>167</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.4">
@@ -2724,7 +2740,7 @@
         <v>168</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.4">
@@ -2735,7 +2751,7 @@
         <v>169</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.4">
@@ -2746,7 +2762,7 @@
         <v>170</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.4">
@@ -2757,7 +2773,7 @@
         <v>171</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.4">
@@ -2768,7 +2784,7 @@
         <v>172</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.4">
@@ -2779,7 +2795,7 @@
         <v>173</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.4">
@@ -2790,7 +2806,7 @@
         <v>174</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.4">
@@ -2801,7 +2817,7 @@
         <v>175</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.4">
@@ -2812,7 +2828,7 @@
         <v>176</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.4">
@@ -2823,7 +2839,7 @@
         <v>177</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.4">
@@ -2831,10 +2847,10 @@
         <v>185</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.4">
@@ -2845,7 +2861,7 @@
         <v>178</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.4">
@@ -2856,7 +2872,7 @@
         <v>179</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.4">
@@ -2867,7 +2883,7 @@
         <v>196</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.4">
@@ -2878,7 +2894,7 @@
         <v>197</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.4">
@@ -2889,7 +2905,7 @@
         <v>198</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.4">
@@ -2900,7 +2916,7 @@
         <v>199</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.4">
@@ -2911,7 +2927,7 @@
         <v>200</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.4">
@@ -2922,7 +2938,7 @@
         <v>201</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.4">
@@ -2933,7 +2949,7 @@
         <v>202</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.4">
@@ -2944,7 +2960,7 @@
         <v>203</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.4">
@@ -2955,7 +2971,7 @@
         <v>204</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.4">
@@ -2966,7 +2982,7 @@
         <v>205</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.4">
@@ -2977,7 +2993,7 @@
         <v>206</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.4">
@@ -2988,7 +3004,7 @@
         <v>207</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.4">
@@ -2999,7 +3015,7 @@
         <v>208</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.4">
@@ -3010,7 +3026,7 @@
         <v>209</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.4">
@@ -3021,7 +3037,7 @@
         <v>210</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.4">
@@ -3032,7 +3048,7 @@
         <v>211</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.4">
@@ -3043,7 +3059,7 @@
         <v>212</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.4">
@@ -3054,7 +3070,7 @@
         <v>110</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.4">
@@ -3065,7 +3081,7 @@
         <v>213</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.4">
@@ -3076,7 +3092,7 @@
         <v>214</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.4">
@@ -3087,7 +3103,7 @@
         <v>215</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.4">
@@ -3098,7 +3114,7 @@
         <v>216</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.4">
@@ -3109,7 +3125,7 @@
         <v>217</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.4">
@@ -3120,7 +3136,7 @@
         <v>218</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.4">
@@ -3131,7 +3147,7 @@
         <v>219</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
@@ -3142,7 +3158,7 @@
         <v>220</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.4">
@@ -3153,7 +3169,7 @@
         <v>132</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.4">
@@ -3164,7 +3180,7 @@
         <v>241</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.4">
@@ -3175,7 +3191,7 @@
         <v>242</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.4">
@@ -3186,7 +3202,7 @@
         <v>243</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.4">
@@ -3197,7 +3213,7 @@
         <v>244</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.4">
@@ -3208,7 +3224,7 @@
         <v>245</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.4">
@@ -3219,7 +3235,7 @@
         <v>11</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.4">
@@ -3230,7 +3246,7 @@
         <v>246</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.4">
@@ -3241,7 +3257,7 @@
         <v>247</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.4">
@@ -3252,7 +3268,7 @@
         <v>248</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.4">
@@ -3263,7 +3279,7 @@
         <v>249</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.4">
@@ -3274,7 +3290,7 @@
         <v>250</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.4">
@@ -3285,7 +3301,7 @@
         <v>251</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.4">
@@ -3296,7 +3312,7 @@
         <v>252</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.4">
@@ -3307,7 +3323,7 @@
         <v>253</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.4">
@@ -3318,18 +3334,18 @@
         <v>254</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A148" s="4" t="s">
+      <c r="A148" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C148" s="5" t="s">
-        <v>401</v>
+      <c r="C148" s="10" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.4">
@@ -3340,7 +3356,7 @@
         <v>256</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.4">
@@ -3351,7 +3367,7 @@
         <v>257</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.4">
@@ -3362,7 +3378,7 @@
         <v>258</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.4">
@@ -3373,7 +3389,7 @@
         <v>259</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.4">
@@ -3384,7 +3400,7 @@
         <v>260</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.4">
@@ -3395,7 +3411,7 @@
         <v>201</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.4">
@@ -3406,7 +3422,7 @@
         <v>71</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.4">
@@ -3417,18 +3433,18 @@
         <v>261</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A157" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.4">
@@ -3439,7 +3455,7 @@
         <v>262</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.4">
@@ -3450,62 +3466,62 @@
         <v>110</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A160" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>281</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A161" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>282</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A162" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>283</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A163" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A164" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>285</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.4">
@@ -3516,29 +3532,29 @@
         <v>286</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A166" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A167" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="B166" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A167" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C167" s="5" t="s">
-        <v>405</v>
+      <c r="C167" s="10" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.4">
@@ -3546,32 +3562,32 @@
         <v>55</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A169" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A170" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.4">
@@ -3579,32 +3595,32 @@
         <v>33</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A172" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A173" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.4">
@@ -3612,10 +3628,10 @@
         <v>187</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.4">
@@ -3623,43 +3639,43 @@
         <v>237</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A176" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A177" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A178" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.4">
@@ -3667,21 +3683,21 @@
         <v>98</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A180" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.4">
@@ -3689,65 +3705,65 @@
         <v>274</v>
       </c>
       <c r="B181" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C181" s="5" t="s">
         <v>404</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A182" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A183" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A184" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A185" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A186" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.4">
@@ -3755,21 +3771,21 @@
         <v>47</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A188" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.4">
@@ -3777,43 +3793,43 @@
         <v>43</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A190" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A191" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A192" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.4">
@@ -3821,10 +3837,10 @@
         <v>47</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.4">
@@ -3832,43 +3848,43 @@
         <v>84</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A195" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A196" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A197" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.4">
@@ -3876,32 +3892,32 @@
         <v>271</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A199" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A200" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.4">
@@ -3912,7 +3928,7 @@
         <v>26</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.4">
@@ -3920,10 +3936,10 @@
         <v>185</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.4">
@@ -3931,10 +3947,10 @@
         <v>33</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.4">
@@ -3942,10 +3958,10 @@
         <v>39</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.4">
@@ -3953,10 +3969,10 @@
         <v>233</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.4">
@@ -3964,65 +3980,65 @@
         <v>98</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A207" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A208" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A209" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A210" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A211" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.4">
@@ -4030,21 +4046,21 @@
         <v>87</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A213" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B213" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C213" s="5" t="s">
         <v>348</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.4">
@@ -4052,21 +4068,21 @@
         <v>134</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A215" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.4">
@@ -4074,10 +4090,10 @@
         <v>274</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.4">
@@ -4085,21 +4101,21 @@
         <v>225</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A218" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.4">
@@ -4107,10 +4123,10 @@
         <v>41</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.4">
@@ -4118,21 +4134,21 @@
         <v>236</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A221" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.4">
@@ -4140,10 +4156,10 @@
         <v>193</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.4">
@@ -4151,10 +4167,10 @@
         <v>89</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.4">
@@ -4165,18 +4181,18 @@
         <v>176</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A225" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.4">
@@ -4184,32 +4200,32 @@
         <v>180</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A227" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A228" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.4">
@@ -4217,10 +4233,10 @@
         <v>182</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.4">
@@ -4228,10 +4244,10 @@
         <v>40</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.4">
@@ -4239,21 +4255,21 @@
         <v>40</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A232" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.4">
@@ -4261,10 +4277,10 @@
         <v>96</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.4">
@@ -4272,10 +4288,10 @@
         <v>142</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.4">
@@ -4283,32 +4299,32 @@
         <v>275</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A236" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A237" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.4">
@@ -4319,29 +4335,29 @@
         <v>81</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A239" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A240" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/students.xlsx
+++ b/students.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\2025.11.26.부터\2025\신입생\신입생반편성\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE8782DB-EF70-4027-8EEE-00A276E1BBB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDEE150-9A8E-49DC-A2F6-A125F45969F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E82CF06-4291-4BB2-932B-E63723969F27}"/>
+    <workbookView xWindow="0" yWindow="165" windowWidth="21600" windowHeight="11295" xr2:uid="{2E82CF06-4291-4BB2-932B-E63723969F27}"/>
   </bookViews>
   <sheets>
     <sheet name="최종명단" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1714,13 +1717,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48541750-A9E2-46B4-830D-4D2F0181A0E7}">
   <dimension ref="A1:C240"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="14.296875" customWidth="1"/>
-    <col min="3" max="3" width="15.3984375" customWidth="1"/>
+    <col min="1" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1731,7 +1734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
@@ -1742,7 +1745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
@@ -1753,7 +1756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
@@ -1764,7 +1767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
@@ -1775,7 +1778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -1786,7 +1789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
@@ -1797,7 +1800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>38</v>
       </c>
@@ -1808,7 +1811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>39</v>
       </c>
@@ -1819,7 +1822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
@@ -1830,7 +1833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>41</v>
       </c>
@@ -1841,7 +1844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>42</v>
       </c>
@@ -1852,7 +1855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -1863,7 +1866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>44</v>
       </c>
@@ -1874,7 +1877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>45</v>
       </c>
@@ -1885,7 +1888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>46</v>
       </c>
@@ -1896,7 +1899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>47</v>
       </c>
@@ -1907,7 +1910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>48</v>
       </c>
@@ -1918,7 +1921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>49</v>
       </c>
@@ -1929,7 +1932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>50</v>
       </c>
@@ -1940,7 +1943,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>51</v>
       </c>
@@ -1951,7 +1954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>52</v>
       </c>
@@ -1962,7 +1965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>53</v>
       </c>
@@ -1973,7 +1976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>54</v>
       </c>
@@ -1984,7 +1987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>55</v>
       </c>
@@ -1995,7 +1998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>56</v>
       </c>
@@ -2006,7 +2009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>57</v>
       </c>
@@ -2017,7 +2020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>83</v>
       </c>
@@ -2028,7 +2031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>84</v>
       </c>
@@ -2039,7 +2042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>85</v>
       </c>
@@ -2050,7 +2053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>86</v>
       </c>
@@ -2061,7 +2064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>87</v>
       </c>
@@ -2072,7 +2075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>88</v>
       </c>
@@ -2083,7 +2086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>89</v>
       </c>
@@ -2094,7 +2097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="21.6" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>106</v>
       </c>
@@ -2105,7 +2108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>90</v>
       </c>
@@ -2116,7 +2119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>91</v>
       </c>
@@ -2127,7 +2130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>92</v>
       </c>
@@ -2138,7 +2141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>93</v>
       </c>
@@ -2149,7 +2152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>237</v>
       </c>
@@ -2160,7 +2163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>94</v>
       </c>
@@ -2171,7 +2174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>95</v>
       </c>
@@ -2182,7 +2185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>96</v>
       </c>
@@ -2193,7 +2196,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>97</v>
       </c>
@@ -2204,7 +2207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>98</v>
       </c>
@@ -2215,7 +2218,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>99</v>
       </c>
@@ -2226,7 +2229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>83</v>
       </c>
@@ -2237,7 +2240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>100</v>
       </c>
@@ -2248,7 +2251,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>101</v>
       </c>
@@ -2259,7 +2262,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>102</v>
       </c>
@@ -2270,7 +2273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>103</v>
       </c>
@@ -2281,7 +2284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>36</v>
       </c>
@@ -2292,7 +2295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>104</v>
       </c>
@@ -2303,7 +2306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>133</v>
       </c>
@@ -2314,7 +2317,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>98</v>
       </c>
@@ -2325,7 +2328,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>134</v>
       </c>
@@ -2336,7 +2339,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>135</v>
       </c>
@@ -2347,7 +2350,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>136</v>
       </c>
@@ -2358,7 +2361,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>134</v>
       </c>
@@ -2369,7 +2372,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>137</v>
       </c>
@@ -2380,7 +2383,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>88</v>
       </c>
@@ -2391,7 +2394,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>138</v>
       </c>
@@ -2402,7 +2405,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2416,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>92</v>
       </c>
@@ -2424,7 +2427,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>140</v>
       </c>
@@ -2435,7 +2438,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>141</v>
       </c>
@@ -2446,7 +2449,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>142</v>
       </c>
@@ -2457,7 +2460,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>143</v>
       </c>
@@ -2468,7 +2471,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>144</v>
       </c>
@@ -2479,7 +2482,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>145</v>
       </c>
@@ -2490,7 +2493,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>146</v>
       </c>
@@ -2501,7 +2504,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>147</v>
       </c>
@@ -2512,7 +2515,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>148</v>
       </c>
@@ -2523,7 +2526,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>149</v>
       </c>
@@ -2534,7 +2537,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>150</v>
       </c>
@@ -2545,7 +2548,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>151</v>
       </c>
@@ -2556,7 +2559,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>152</v>
       </c>
@@ -2567,7 +2570,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>153</v>
       </c>
@@ -2578,7 +2581,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>58</v>
       </c>
@@ -2589,7 +2592,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>180</v>
       </c>
@@ -2600,7 +2603,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>181</v>
       </c>
@@ -2611,7 +2614,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>34</v>
       </c>
@@ -2622,7 +2625,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>182</v>
       </c>
@@ -2633,7 +2636,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>183</v>
       </c>
@@ -2644,7 +2647,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>145</v>
       </c>
@@ -2655,7 +2658,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>143</v>
       </c>
@@ -2666,7 +2669,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>184</v>
       </c>
@@ -2677,7 +2680,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>133</v>
       </c>
@@ -2688,7 +2691,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>185</v>
       </c>
@@ -2699,7 +2702,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>186</v>
       </c>
@@ -2710,7 +2713,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>187</v>
       </c>
@@ -2721,7 +2724,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>188</v>
       </c>
@@ -2732,7 +2735,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>189</v>
       </c>
@@ -2743,7 +2746,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>190</v>
       </c>
@@ -2754,7 +2757,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>191</v>
       </c>
@@ -2765,7 +2768,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>192</v>
       </c>
@@ -2776,7 +2779,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>193</v>
       </c>
@@ -2787,7 +2790,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>182</v>
       </c>
@@ -2798,7 +2801,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>97</v>
       </c>
@@ -2809,7 +2812,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>194</v>
       </c>
@@ -2820,7 +2823,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>195</v>
       </c>
@@ -2831,7 +2834,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>96</v>
       </c>
@@ -2842,7 +2845,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
         <v>185</v>
       </c>
@@ -2853,7 +2856,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>55</v>
       </c>
@@ -2864,7 +2867,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>55</v>
       </c>
@@ -2872,10 +2875,10 @@
         <v>179</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>221</v>
       </c>
@@ -2886,7 +2889,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>149</v>
       </c>
@@ -2897,7 +2900,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>222</v>
       </c>
@@ -2908,7 +2911,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>98</v>
       </c>
@@ -2919,7 +2922,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>145</v>
       </c>
@@ -2930,7 +2933,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>54</v>
       </c>
@@ -2941,7 +2944,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>104</v>
       </c>
@@ -2952,7 +2955,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>223</v>
       </c>
@@ -2963,7 +2966,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>224</v>
       </c>
@@ -2974,7 +2977,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>225</v>
       </c>
@@ -2985,7 +2988,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>226</v>
       </c>
@@ -2996,7 +2999,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>227</v>
       </c>
@@ -3007,7 +3010,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>228</v>
       </c>
@@ -3018,7 +3021,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>229</v>
       </c>
@@ -3029,7 +3032,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>230</v>
       </c>
@@ -3040,7 +3043,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>231</v>
       </c>
@@ -3051,7 +3054,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>49</v>
       </c>
@@ -3062,7 +3065,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>232</v>
       </c>
@@ -3073,7 +3076,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>233</v>
       </c>
@@ -3084,7 +3087,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>234</v>
       </c>
@@ -3095,7 +3098,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>235</v>
       </c>
@@ -3106,7 +3109,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>236</v>
       </c>
@@ -3117,7 +3120,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>237</v>
       </c>
@@ -3128,7 +3131,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>238</v>
       </c>
@@ -3139,7 +3142,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>239</v>
       </c>
@@ -3150,7 +3153,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>240</v>
       </c>
@@ -3161,7 +3164,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>154</v>
       </c>
@@ -3172,7 +3175,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>141</v>
       </c>
@@ -3183,7 +3186,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>263</v>
       </c>
@@ -3194,7 +3197,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>264</v>
       </c>
@@ -3205,7 +3208,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>265</v>
       </c>
@@ -3216,7 +3219,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>266</v>
       </c>
@@ -3227,7 +3230,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>185</v>
       </c>
@@ -3238,7 +3241,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>188</v>
       </c>
@@ -3249,7 +3252,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>54</v>
       </c>
@@ -3260,7 +3263,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>267</v>
       </c>
@@ -3271,7 +3274,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>268</v>
       </c>
@@ -3282,7 +3285,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>269</v>
       </c>
@@ -3293,7 +3296,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>270</v>
       </c>
@@ -3304,7 +3307,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>187</v>
       </c>
@@ -3315,7 +3318,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>271</v>
       </c>
@@ -3326,7 +3329,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>137</v>
       </c>
@@ -3337,7 +3340,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
         <v>272</v>
       </c>
@@ -3348,7 +3351,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>273</v>
       </c>
@@ -3359,7 +3362,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>274</v>
       </c>
@@ -3370,7 +3373,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>275</v>
       </c>
@@ -3381,7 +3384,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>276</v>
       </c>
@@ -3392,7 +3395,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>277</v>
       </c>
@@ -3403,7 +3406,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>278</v>
       </c>
@@ -3414,7 +3417,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>279</v>
       </c>
@@ -3425,7 +3428,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>237</v>
       </c>
@@ -3436,7 +3439,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
         <v>402</v>
       </c>
@@ -3447,7 +3450,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>280</v>
       </c>
@@ -3458,7 +3461,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>191</v>
       </c>
@@ -3469,7 +3472,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>305</v>
       </c>
@@ -3480,7 +3483,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>306</v>
       </c>
@@ -3491,7 +3494,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>307</v>
       </c>
@@ -3502,7 +3505,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>308</v>
       </c>
@@ -3513,7 +3516,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>309</v>
       </c>
@@ -3524,7 +3527,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>154</v>
       </c>
@@ -3535,7 +3538,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>310</v>
       </c>
@@ -3546,7 +3549,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
         <v>311</v>
       </c>
@@ -3557,7 +3560,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>55</v>
       </c>
@@ -3568,7 +3571,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>312</v>
       </c>
@@ -3579,7 +3582,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>313</v>
       </c>
@@ -3590,7 +3593,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>33</v>
       </c>
@@ -3601,7 +3604,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>314</v>
       </c>
@@ -3612,7 +3615,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>315</v>
       </c>
@@ -3623,7 +3626,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
         <v>187</v>
       </c>
@@ -3634,7 +3637,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>237</v>
       </c>
@@ -3645,7 +3648,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
         <v>316</v>
       </c>
@@ -3656,7 +3659,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
         <v>317</v>
       </c>
@@ -3667,7 +3670,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
         <v>318</v>
       </c>
@@ -3678,7 +3681,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
         <v>98</v>
       </c>
@@ -3689,7 +3692,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
         <v>319</v>
       </c>
@@ -3700,7 +3703,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
         <v>274</v>
       </c>
@@ -3711,7 +3714,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
         <v>320</v>
       </c>
@@ -3722,7 +3725,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
         <v>321</v>
       </c>
@@ -3733,7 +3736,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
         <v>322</v>
       </c>
@@ -3744,7 +3747,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
         <v>319</v>
       </c>
@@ -3755,7 +3758,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
         <v>315</v>
       </c>
@@ -3766,7 +3769,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
         <v>47</v>
       </c>
@@ -3777,7 +3780,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
         <v>349</v>
       </c>
@@ -3788,7 +3791,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
         <v>43</v>
       </c>
@@ -3799,7 +3802,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
         <v>305</v>
       </c>
@@ -3810,7 +3813,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
         <v>350</v>
       </c>
@@ -3821,7 +3824,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
         <v>351</v>
       </c>
@@ -3832,7 +3835,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>47</v>
       </c>
@@ -3843,7 +3846,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
         <v>84</v>
       </c>
@@ -3854,7 +3857,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
         <v>352</v>
       </c>
@@ -3865,7 +3868,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
         <v>317</v>
       </c>
@@ -3876,7 +3879,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
         <v>353</v>
       </c>
@@ -3887,7 +3890,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
         <v>271</v>
       </c>
@@ -3898,7 +3901,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
         <v>354</v>
       </c>
@@ -3909,7 +3912,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
         <v>355</v>
       </c>
@@ -3920,7 +3923,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
         <v>185</v>
       </c>
@@ -3931,7 +3934,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>185</v>
       </c>
@@ -3942,7 +3945,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>33</v>
       </c>
@@ -3953,7 +3956,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>39</v>
       </c>
@@ -3964,7 +3967,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>233</v>
       </c>
@@ -3975,7 +3978,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>98</v>
       </c>
@@ -3986,7 +3989,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>356</v>
       </c>
@@ -3997,7 +4000,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>357</v>
       </c>
@@ -4008,7 +4011,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>358</v>
       </c>
@@ -4019,7 +4022,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>317</v>
       </c>
@@ -4030,7 +4033,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>359</v>
       </c>
@@ -4041,7 +4044,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>87</v>
       </c>
@@ -4052,7 +4055,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>360</v>
       </c>
@@ -4063,7 +4066,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>134</v>
       </c>
@@ -4074,7 +4077,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>386</v>
       </c>
@@ -4085,7 +4088,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>274</v>
       </c>
@@ -4096,7 +4099,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
         <v>225</v>
       </c>
@@ -4107,7 +4110,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>387</v>
       </c>
@@ -4118,7 +4121,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>41</v>
       </c>
@@ -4129,7 +4132,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>236</v>
       </c>
@@ -4140,7 +4143,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>388</v>
       </c>
@@ -4151,7 +4154,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>193</v>
       </c>
@@ -4162,7 +4165,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>89</v>
       </c>
@@ -4173,7 +4176,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>43</v>
       </c>
@@ -4184,7 +4187,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>389</v>
       </c>
@@ -4195,7 +4198,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>180</v>
       </c>
@@ -4206,7 +4209,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>390</v>
       </c>
@@ -4217,7 +4220,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>306</v>
       </c>
@@ -4228,7 +4231,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>182</v>
       </c>
@@ -4239,7 +4242,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>40</v>
       </c>
@@ -4250,7 +4253,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
         <v>40</v>
       </c>
@@ -4261,7 +4264,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
         <v>319</v>
       </c>
@@ -4272,7 +4275,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
         <v>96</v>
       </c>
@@ -4283,7 +4286,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>142</v>
       </c>
@@ -4294,7 +4297,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>275</v>
       </c>
@@ -4305,7 +4308,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>391</v>
       </c>
@@ -4316,7 +4319,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>392</v>
       </c>
@@ -4327,7 +4330,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>278</v>
       </c>
@@ -4338,7 +4341,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>393</v>
       </c>
@@ -4349,7 +4352,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>394</v>
       </c>
